--- a/cad/tests/综合测试analysis/print_info_analysis.xlsx
+++ b/cad/tests/综合测试analysis/print_info_analysis.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>D:\codex-tasks\cad\tests\综合测试.dwg</t>
+          <t>D:\codex-tasks\cad\tests\综合测试 - 0416.dwg</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -567,13 +567,13 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
@@ -587,7 +587,7 @@
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="12" customWidth="1" min="36" max="36"/>
-    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,6 +774,1266 @@
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>分析终止原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-01</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>81DA</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A2_(594.00_x_420.00_MM)</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>no_inner_frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-02</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>81F9</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>A2+3/4</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>UserDefinedMetric (1041.00 x 420.00毫米)</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="2" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>portrait</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>no_inner_frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-03</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8219</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A2_(594.00_x_420.00_MM)</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>no_inner_frame</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-04</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4DEE</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>4DEF</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>(-310.9841886581021, 711.1662634268639, 74.01581134189792, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-05</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4E16</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>4E17</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>(162.85949222645468, 711.1662634268639, 547.8594922264547, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-06</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4E1C</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>4E1D</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>(645.7992503808168, 711.1662634268639, 1030.7992503808168, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4E22</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>4E23</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>(1144.2819015391678, 711.1662634268639, 1529.2819015391678, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-08</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4E4C</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>4E4D</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>(1642.7645526975189, 711.1662634268639, 2027.7645526975189, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-09</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4E52</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>4E53</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>(2141.24720385587, 711.1662634268639, 2526.24720385587, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4E58</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>4E59</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>(2693.981700808951, 711.1662634268637, 2970.9817008089512, 1096.1662634268637)</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>portrait</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-11</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4E60</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>4E61</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>(3138.212506172572, 711.1662634268639, 3523.212506172572, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图-12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>平面分割图</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4E66</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1:100</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>ISO_A3_(420.00_x_297.00_MM)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>4E67</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>(3636.695157330923, 711.1662634268639, 4021.695157330923, 988.1662634268639)</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>landscape</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>no_corner_block</t>
         </is>
       </c>
     </row>
